--- a/器材报价表.xlsx
+++ b/器材报价表.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>STM32F03C8T6</t>
   </si>
@@ -37,9 +37,6 @@
     <t>HC05蓝牙模块</t>
   </si>
   <si>
-    <t>无源蜂鸣器</t>
-  </si>
-  <si>
     <t>LR7843</t>
   </si>
   <si>
@@ -53,6 +50,30 @@
   </si>
   <si>
     <t>VL53L0XV2激光测距</t>
+  </si>
+  <si>
+    <t>5.1k电阻</t>
+  </si>
+  <si>
+    <t>100电阻</t>
+  </si>
+  <si>
+    <t>10k电阻</t>
+  </si>
+  <si>
+    <t>100nf电容</t>
+  </si>
+  <si>
+    <t>10uf电容</t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
+    <t>AMS1117</t>
+  </si>
+  <si>
+    <t>排母</t>
   </si>
 </sst>
 </file>
@@ -983,8 +1004,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="1"/>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="25.7636363636364" customWidth="1"/>
     <col min="2" max="2" width="10.7" customWidth="1"/>
@@ -1011,7 +1032,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1027,7 +1048,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1035,7 +1056,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1043,7 +1064,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1051,7 +1072,63 @@
         <v>7</v>
       </c>
       <c r="B8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
         <v>11</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
